--- a/040625-skills.xlsx
+++ b/040625-skills.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Documents\claude_projects\sd_github_021626\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\629459\Documents\_ AGENTIC AI Technologist\_projects_cursor\daily_tasks_030426\github-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A16110-ACBB-4DBD-B044-AC8D9B16C0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8084A1-ECF2-4D34-A3F7-092F735566F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="216">
   <si>
     <t>e_id</t>
   </si>
@@ -750,12 +750,24 @@
   <si>
     <t>Claude Code - GitHub Deployment Workflow</t>
   </si>
+  <si>
+    <t>Splunk (from Cisco) | Using Fields</t>
+  </si>
+  <si>
+    <t>Splunk (from Cisco)</t>
+  </si>
+  <si>
+    <t>splunk enterprise (from cisco)</t>
+  </si>
+  <si>
+    <t>splunk search processing language (spl)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -832,6 +844,11 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -854,7 +871,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,6 +962,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1164,7 +1184,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z72"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
@@ -3936,12 +3956,44 @@
         <v>150</v>
       </c>
     </row>
+    <row r="73" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A73" s="3">
+        <v>84</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="12">
+        <v>46240</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="E73" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="M73" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="P73" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U42">
     <sortCondition ref="A2:A42"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36:B39 B41 B32:B34 B2:B28 B61:B70" xr:uid="{ED44EAAA-DACA-40E8-A7DB-D96063B10E1E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36:B39 B41 B32:B34 B2:B28 B61:B70 B73" xr:uid="{ED44EAAA-DACA-40E8-A7DB-D96063B10E1E}">
       <formula1>$T$3:$T$8</formula1>
     </dataValidation>
   </dataValidations>

--- a/040625-skills.xlsx
+++ b/040625-skills.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\629459\Documents\_ AGENTIC AI Technologist\_projects_cursor\daily_tasks_030426\github-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8084A1-ECF2-4D34-A3F7-092F735566F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B97897F-1253-4915-ABFC-491E825930E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="218">
   <si>
     <t>e_id</t>
   </si>
@@ -762,12 +762,18 @@
   <si>
     <t>splunk search processing language (spl)</t>
   </si>
+  <si>
+    <t>devops</t>
+  </si>
+  <si>
+    <t>Splunk Enterprise (from Cisco) | Visualizations</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -793,12 +799,6 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;Aptos Narrow&quot;"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -813,41 +813,49 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="&quot;Aptos Narrow&quot;"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -869,9 +877,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -889,19 +897,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -913,57 +912,77 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1184,2807 +1203,2731 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="42.140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="22" style="23" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" style="19" customWidth="1"/>
-    <col min="7" max="8" width="12.5703125" style="19"/>
-    <col min="9" max="9" width="17.42578125" style="19" customWidth="1"/>
-    <col min="10" max="12" width="12.5703125" style="19"/>
-    <col min="13" max="13" width="17.85546875" style="19" customWidth="1"/>
-    <col min="14" max="14" width="24.7109375" style="14" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" style="19" customWidth="1"/>
-    <col min="16" max="17" width="16.42578125" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="19" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="36" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="22" style="31" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="20" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="20"/>
+    <col min="9" max="9" width="17.42578125" style="20" customWidth="1"/>
+    <col min="10" max="12" width="12.5703125" style="20"/>
+    <col min="13" max="13" width="17.85546875" style="20" customWidth="1"/>
+    <col min="14" max="14" width="24.7109375" style="19" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="20" customWidth="1"/>
+    <col min="16" max="17" width="16.42578125" style="22" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="22"/>
+    <col min="19" max="19" width="15.140625" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="12.5703125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2" spans="1:26" ht="114">
-      <c r="A2" s="3">
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+    </row>
+    <row r="2" spans="1:26" ht="120">
+      <c r="A2" s="29">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="30">
         <v>45734</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="32">
         <v>2</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" t="s">
+      <c r="P2" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" t="s">
+      <c r="T2" s="22" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="256.5">
-      <c r="A3" s="3">
+    <row r="3" spans="1:26" ht="300">
+      <c r="A3" s="29">
         <v>7</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="30">
         <v>45741</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="10"/>
-      <c r="P3" t="s">
+      <c r="P3" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="199.5">
-      <c r="A4" s="3">
+    <row r="4" spans="1:26" ht="225">
+      <c r="A4" s="29">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="30">
         <v>45718</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="T4" s="25" t="s">
+      <c r="T4" s="22" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="409.5">
-      <c r="A5" s="3">
+      <c r="A5" s="29">
         <v>10</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="30">
         <v>35855</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="22">
         <v>2</v>
       </c>
-      <c r="S5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="409.5">
-      <c r="A6" s="3">
+      <c r="A6" s="29">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="30">
         <v>35855</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="409.5">
-      <c r="A7" s="3">
+      <c r="A7" s="29">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="30">
         <v>35855</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="P7" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="Q7" s="19" t="s">
+      <c r="Q7" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="409.5">
-      <c r="A8" s="3">
+      <c r="A8" s="29">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="30">
         <v>35855</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="Q8" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4" t="s">
+      <c r="T8" s="22" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="30" customHeight="1">
-      <c r="A9" s="3">
+      <c r="A9" s="29">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="30">
         <v>44531</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="E9" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N9" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T9" s="22" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="30" customHeight="1">
-      <c r="A10" s="3">
+      <c r="A10" s="29">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="30">
         <v>44614</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N10" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T10" s="22" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="30" customHeight="1">
-      <c r="A11" s="3">
+      <c r="A11" s="29">
         <v>16</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="30">
         <v>44795</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
+      <c r="E11" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="22" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="28.5">
-      <c r="A12" s="3">
+    <row r="12" spans="1:26" ht="45">
+      <c r="A12" s="29">
         <v>17</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="30">
         <v>44795</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="E12" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="N12" s="18" t="s">
+      <c r="N12" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q12" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="T12" s="4" t="s">
+      <c r="T12" s="22" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="89.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:26" ht="120">
+      <c r="A13" s="29">
         <v>18</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="35">
         <v>45242</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="E13" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="Q13" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="114">
-      <c r="A14" s="3">
+    <row r="14" spans="1:26" ht="120">
+      <c r="A14" s="29">
         <v>19</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="35">
         <v>44911</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="E14" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10" t="s">
+      <c r="M14" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N14" s="18" t="s">
+      <c r="N14" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="Q14" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="114">
-      <c r="A15" s="3">
+    <row r="15" spans="1:26" ht="120">
+      <c r="A15" s="29">
         <v>23</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="30">
         <v>44958</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="E15" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10" t="s">
+      <c r="M15" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="N15" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="Q15" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="42.75">
-      <c r="A16" s="3">
+    <row r="16" spans="1:26" ht="45">
+      <c r="A16" s="29">
         <v>24</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="30">
         <v>44986</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="E16" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="N16" s="18" t="s">
+      <c r="N16" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q16" s="22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="114">
-      <c r="A17" s="3">
+    <row r="17" spans="1:19" ht="120">
+      <c r="A17" s="29">
         <v>25</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="30">
         <v>45078</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="E17" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N17" s="18" t="s">
+      <c r="N17" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P17" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q17" s="22" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="114">
-      <c r="A18" s="3">
+    <row r="18" spans="1:19" ht="120">
+      <c r="A18" s="29">
         <v>26</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="30">
         <v>45047</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="E18" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N18" s="18" t="s">
+      <c r="N18" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P18" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q18" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="57">
-      <c r="A19" s="3">
+    <row r="19" spans="1:19" ht="75">
+      <c r="A19" s="29">
         <v>27</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="30">
         <v>45078</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="E19" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N19" s="18" t="s">
+      <c r="N19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q19" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="57">
-      <c r="A20" s="3">
+    <row r="20" spans="1:19" ht="75">
+      <c r="A20" s="29">
         <v>28</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="30">
         <v>45078</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G20" s="10" t="s">
+      <c r="E20" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10" t="s">
+      <c r="M20" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N20" s="18" t="s">
+      <c r="N20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q20" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="114">
-      <c r="A21" s="3">
+    <row r="21" spans="1:19" ht="120">
+      <c r="A21" s="29">
         <v>29</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="30">
         <v>45108</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="E21" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10" t="s">
+      <c r="M21" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N21" s="18" t="s">
+      <c r="N21" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q21" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="114">
-      <c r="A22" s="3">
+    <row r="22" spans="1:19" ht="120">
+      <c r="A22" s="29">
         <v>30</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="30">
         <v>45231</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G22" s="10" t="s">
+      <c r="E22" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10" t="s">
+      <c r="M22" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="N22" s="18" t="s">
+      <c r="N22" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P22" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q22" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="57">
-      <c r="A23" s="3">
+    <row r="23" spans="1:19" ht="60">
+      <c r="A23" s="29">
         <v>31</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="30">
         <v>45292</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="E23" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10" t="s">
+      <c r="M23" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N23" s="18" t="s">
+      <c r="N23" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P23" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q23" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="S23" t="s">
+      <c r="S23" s="22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="57">
-      <c r="A24" s="3">
+    <row r="24" spans="1:19" ht="60">
+      <c r="A24" s="29">
         <v>32</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="30">
         <v>45323</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10" t="s">
+      <c r="E24" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10" t="s">
+      <c r="M24" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N24" s="18" t="s">
+      <c r="N24" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P24" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="Q24" s="22" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="57">
-      <c r="A25" s="3">
+    <row r="25" spans="1:19" ht="60">
+      <c r="A25" s="29">
         <v>33</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="30">
         <v>45323</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10" t="s">
+      <c r="E25" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10" t="s">
+      <c r="M25" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N25" s="18" t="s">
+      <c r="N25" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P25" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="Q25" s="22" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="51">
-      <c r="A26" s="3">
+    <row r="26" spans="1:19" ht="75">
+      <c r="A26" s="29">
         <v>34</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="30">
         <v>45293</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G26" s="10" t="s">
+      <c r="E26" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10" t="s">
+      <c r="M26" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N26" s="24" t="s">
+      <c r="N26" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="P26" t="s">
+      <c r="P26" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="Q26" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="57">
-      <c r="A27" s="3">
+    <row r="27" spans="1:19" ht="60">
+      <c r="A27" s="29">
         <v>35</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="30">
         <v>45261</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G27" s="10" t="s">
+      <c r="E27" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10" t="s">
+      <c r="M27" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N27" s="18" t="s">
+      <c r="N27" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P27" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="Q27" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="28.5">
-      <c r="A28" s="3">
+    <row r="28" spans="1:19" ht="30">
+      <c r="A28" s="29">
         <v>36</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="30">
         <v>45627</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G28" s="10" t="s">
+      <c r="E28" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10" t="s">
+      <c r="M28" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="N28" s="18" t="s">
+      <c r="N28" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P28" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="Q28" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="14.25">
-      <c r="A29" s="3">
+    <row r="29" spans="1:19" ht="15">
+      <c r="A29" s="29">
         <v>38</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="30">
         <v>45689</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="E29" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10" t="s">
+      <c r="M29" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O29" s="10"/>
-      <c r="P29" t="s">
+      <c r="P29" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="Q29" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-    </row>
-    <row r="30" spans="1:19" ht="114">
-      <c r="A30" s="3">
+    </row>
+    <row r="30" spans="1:19" ht="135">
+      <c r="A30" s="29">
         <v>39</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="30">
         <v>45717</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G30" s="10" t="s">
+      <c r="E30" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10" t="s">
+      <c r="M30" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="N30" s="18" t="s">
+      <c r="N30" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P30" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="Q30" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="S30" t="s">
+      <c r="S30" s="22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="28.5">
-      <c r="A31" s="3">
+    <row r="31" spans="1:19" ht="45">
+      <c r="A31" s="29">
         <v>40</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="30">
         <v>45717</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F31" s="19">
+      <c r="E31" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="20">
         <v>1</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="19" t="s">
+      <c r="M31" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="N31" s="18" t="s">
+      <c r="N31" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P31" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="Q31" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="S31" t="s">
+      <c r="S31" s="22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="14.25">
-      <c r="A32" s="3">
+    <row r="32" spans="1:19" ht="15">
+      <c r="A32" s="29">
         <v>41</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="30">
         <v>45717</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G32" s="10" t="s">
+      <c r="E32" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10" t="s">
+      <c r="M32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="N32" s="8"/>
-      <c r="O32" s="10"/>
-      <c r="P32" t="s">
+      <c r="P32" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="Q32" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:19" ht="53.25" customHeight="1">
-      <c r="A33" s="3">
+      <c r="A33" s="29">
         <v>42</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="36">
         <v>45752</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="M33" s="22" t="s">
+      <c r="M33" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="P33" s="19" t="s">
+      <c r="P33" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q33" s="19" t="s">
+      <c r="Q33" s="20" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A34" s="3">
+      <c r="A34" s="29">
         <v>43</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="36">
         <v>45776</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="19" t="s">
+      <c r="I34" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M34" s="19" t="s">
+      <c r="M34" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O34"/>
-      <c r="P34" t="s">
+      <c r="O34" s="22"/>
+      <c r="P34" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="Q34" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="14.25">
-      <c r="A35" s="3">
+    <row r="35" spans="1:19" ht="15">
+      <c r="A35" s="29">
         <v>44</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="36">
         <v>45748</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" s="19">
+      <c r="E35" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="20">
         <v>1</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="M35" s="19" t="s">
+      <c r="M35" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P35" t="s">
+      <c r="P35" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="Q35" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="S35" t="s">
+      <c r="S35" s="22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="127.5">
-      <c r="A36" s="3">
+    <row r="36" spans="1:19" ht="195">
+      <c r="A36" s="29">
         <v>45</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="36">
         <v>45748</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="I36" s="19" t="s">
+      <c r="I36" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="J36" s="19" t="s">
+      <c r="J36" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P36" s="19" t="s">
+      <c r="P36" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q36" s="19" t="s">
+      <c r="Q36" s="20" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="51">
-      <c r="A37" s="3">
+    <row r="37" spans="1:19" ht="75">
+      <c r="A37" s="29">
         <v>46</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="36">
         <v>45869</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="F37" s="19">
+      <c r="E37" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="20">
         <v>2</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="19" t="s">
+      <c r="J37" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K37" s="19" t="s">
+      <c r="K37" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="M37" s="19" t="s">
+      <c r="M37" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="N37" s="14" t="s">
+      <c r="N37" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="Q37" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="22">
         <v>4</v>
       </c>
-      <c r="S37" t="s">
+      <c r="S37" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A38" s="3">
+      <c r="A38" s="29">
         <v>48</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="36">
         <v>45905</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F38" s="19">
+      <c r="E38" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F38" s="20">
         <v>2</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M38" s="19" t="s">
+      <c r="M38" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="N38" s="14" t="s">
+      <c r="N38" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="P38" t="s">
+      <c r="P38" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="Q38" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A39" s="3">
+      <c r="A39" s="29">
         <v>49</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="36">
         <v>45908</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G39" s="22" t="s">
+      <c r="E39" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="M39" s="19" t="s">
+      <c r="M39" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N39" s="24" t="s">
+      <c r="N39" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P39" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="Q39" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="27" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A40" s="26">
+    <row r="40" spans="1:19" s="21" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A40" s="37">
         <v>50</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="38">
         <v>45910</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="E40" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="F40" s="30">
+      <c r="E40" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" s="40">
         <v>1</v>
       </c>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="19" t="s">
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="N40" s="31"/>
-      <c r="O40" s="30"/>
-      <c r="P40" t="s">
+      <c r="N40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="Q40" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="R40" s="27">
+      <c r="R40" s="21">
         <v>1</v>
       </c>
-      <c r="S40" s="27" t="s">
+      <c r="S40" s="21" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A41" s="3">
+      <c r="A41" s="29">
         <v>51</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="36">
         <v>45352</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E41" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="19">
+      <c r="E41" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" s="20">
         <v>3</v>
       </c>
-      <c r="G41" s="19" t="s">
+      <c r="G41" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="I41" s="19" t="s">
+      <c r="I41" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M41" s="19" t="s">
+      <c r="M41" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="N41" s="14" t="s">
+      <c r="N41" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="Q41" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="S41" t="s">
+      <c r="S41" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A42" s="3">
+      <c r="A42" s="29">
         <v>52</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="36">
         <v>45717</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="E42" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="F42" s="19">
+      <c r="E42" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="20">
         <v>3</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="G42" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="H42" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I42" s="19" t="s">
+      <c r="I42" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="M42" s="19" t="s">
+      <c r="M42" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="Q42" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="S42" t="s">
+      <c r="S42" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A43" s="3">
+      <c r="A43" s="29">
         <v>53</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="36">
         <v>45910</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="E43" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="M43" s="19" t="s">
+      <c r="E43" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="M43" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="Q43" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="22">
         <v>2</v>
       </c>
-      <c r="S43" t="s">
+      <c r="S43" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A44" s="3">
+      <c r="A44" s="29">
         <v>54</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E44" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="E44" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="H44" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="J44" s="19" t="s">
+      <c r="J44" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="K44" s="19" t="s">
+      <c r="K44" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="M44" s="19" t="s">
+      <c r="M44" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="Q44" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A45" s="3">
+      <c r="A45" s="29">
         <v>55</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="E45" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="E45" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M45" s="19" t="s">
+      <c r="M45" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P45" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="Q45" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A46" s="3">
+      <c r="A46" s="29">
         <v>56</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E46" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="E46" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G46" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M46" s="19" t="s">
+      <c r="M46" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="Q46" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A47" s="3">
+      <c r="A47" s="29">
         <v>57</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="E47" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="E47" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M47" s="19" t="s">
+      <c r="M47" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P47" t="s">
+      <c r="P47" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="Q47" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A48" s="3">
+      <c r="A48" s="29">
         <v>58</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="E48" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G48" t="s">
+      <c r="E48" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M48" s="19" t="s">
+      <c r="M48" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P48" t="s">
+      <c r="P48" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q48" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A49" s="3">
+      <c r="A49" s="29">
         <v>59</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="E49" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="E49" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G49" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="M49" s="19" t="s">
+      <c r="M49" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="P49" t="s">
+      <c r="P49" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="Q49" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A50" s="3">
+      <c r="A50" s="29">
         <v>60</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="E50" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="E50" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M50" s="19" t="s">
+      <c r="M50" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="P50" t="s">
+      <c r="P50" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="Q50" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A51" s="3">
+      <c r="A51" s="29">
         <v>61</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E51" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="E51" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M51" s="19" t="s">
+      <c r="M51" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="P51" t="s">
+      <c r="P51" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="Q51" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A52" s="3">
+      <c r="A52" s="29">
         <v>62</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E52" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="E52" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G52" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="M52" s="10" t="s">
+      <c r="M52" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="P52" t="s">
+      <c r="P52" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="Q52" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A53" s="3">
+      <c r="A53" s="29">
         <v>63</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="E53" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="E53" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G53" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="I53" s="19" t="s">
+      <c r="I53" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="M53" s="19" t="s">
+      <c r="M53" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="P53" t="s">
+      <c r="P53" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="Q53" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A54" s="3">
+      <c r="A54" s="29">
         <v>64</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="E54" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G54" s="19" t="s">
+      <c r="E54" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G54" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M54" s="19" t="s">
+      <c r="M54" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P54" t="s">
+      <c r="P54" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="Q54" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R54">
+      <c r="R54" s="22">
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A55" s="3">
+      <c r="A55" s="29">
         <v>65</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="E55" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G55" s="19" t="s">
+      <c r="E55" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G55" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="H55" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="I55" s="19" t="s">
+      <c r="I55" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="J55" s="25" t="s">
+      <c r="J55" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="M55" s="19" t="s">
+      <c r="M55" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P55" t="s">
+      <c r="P55" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="Q55" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R55">
+      <c r="R55" s="22">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A56" s="3">
+      <c r="A56" s="29">
         <v>66</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="E56" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="E56" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G56" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K56" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="M56" s="19" t="s">
+      <c r="M56" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P56" t="s">
+      <c r="P56" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="Q56" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A57" s="3">
+      <c r="A57" s="29">
         <v>67</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="E57" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G57" s="25" t="s">
+      <c r="E57" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G57" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="M57" s="19" t="s">
+      <c r="M57" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P57" t="s">
+      <c r="P57" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="Q57" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R57">
+      <c r="R57" s="22">
         <v>3</v>
       </c>
-      <c r="S57" t="s">
+      <c r="S57" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A58" s="3">
+      <c r="A58" s="29">
         <v>68</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D58" s="33" t="s">
+      <c r="D58" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E58" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G58" s="25" t="s">
+      <c r="E58" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G58" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="M58" s="19" t="s">
+      <c r="M58" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P58" t="s">
+      <c r="P58" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="Q58" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R58">
+      <c r="R58" s="22">
         <v>4</v>
       </c>
-      <c r="S58" t="s">
+      <c r="S58" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A59" s="3">
+      <c r="A59" s="29">
         <v>69</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D59" s="33" t="s">
+      <c r="D59" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="E59" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G59" s="25" t="s">
+      <c r="E59" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G59" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="J59" s="19" t="s">
+      <c r="J59" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="K59" s="19" t="s">
+      <c r="K59" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="M59" s="19" t="s">
+      <c r="M59" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P59" t="s">
+      <c r="P59" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="Q59" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="22">
         <v>4</v>
       </c>
-      <c r="S59" t="s">
+      <c r="S59" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A60" s="3">
+      <c r="A60" s="29">
         <v>70</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="34" t="s">
+      <c r="D60" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="E60" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="E60" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G60" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H60" s="19" t="s">
+      <c r="H60" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M60" s="19" t="s">
+      <c r="M60" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P60" t="s">
+      <c r="P60" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="Q60" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="22">
         <v>4</v>
       </c>
-      <c r="S60" t="s">
+      <c r="S60" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A61" s="3">
+      <c r="A61" s="29">
         <v>71</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="34" t="s">
+      <c r="D61" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="E61" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="E61" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G61" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="H61" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M61" s="19" t="s">
+      <c r="M61" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P61" t="s">
+      <c r="P61" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="Q61" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="22">
         <v>4</v>
       </c>
-      <c r="S61" t="s">
+      <c r="S61" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A62" s="3">
+      <c r="A62" s="29">
         <v>72</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="36">
         <v>45678</v>
       </c>
-      <c r="D62" s="34" t="s">
+      <c r="D62" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="M62" s="19" t="s">
+      <c r="E62" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="M62" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P62" t="s">
+      <c r="P62" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="Q62" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="R62">
+      <c r="R62" s="22">
         <v>4</v>
       </c>
-      <c r="S62" t="s">
+      <c r="S62" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A63" s="3">
+      <c r="A63" s="29">
         <v>73</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="36">
         <v>45645</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D63" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E63" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-      <c r="M63" s="19" t="s">
+      <c r="E63" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="M63" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P63" t="s">
+      <c r="P63" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="Q63" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A64" s="3">
+      <c r="A64" s="29">
         <v>74</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="36">
         <v>45534</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E64" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="M64" s="19" t="s">
+      <c r="E64" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="M64" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P64" t="s">
+      <c r="P64" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="Q64" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A65" s="3">
+      <c r="A65" s="29">
         <v>75</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="36">
         <v>45467</v>
       </c>
-      <c r="D65" s="34" t="s">
+      <c r="D65" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="E65" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="M65" s="19" t="s">
+      <c r="E65" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="M65" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P65" t="s">
+      <c r="P65" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="Q65" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A66" s="3">
+      <c r="A66" s="29">
         <v>76</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="36">
         <v>44973</v>
       </c>
-      <c r="D66" s="34" t="s">
+      <c r="D66" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="E66" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="M66" s="19" t="s">
+      <c r="E66" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
+      <c r="M66" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P66" t="s">
+      <c r="P66" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="Q66" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A67" s="3">
+      <c r="A67" s="29">
         <v>77</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="36">
         <v>45930</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="E67" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="M67" s="19" t="s">
+      <c r="E67" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
+      <c r="M67" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P67" t="s">
+      <c r="P67" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="Q67" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="R67">
+      <c r="R67" s="22">
         <v>1</v>
       </c>
-      <c r="S67" t="s">
+      <c r="S67" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A68" s="3">
+      <c r="A68" s="29">
         <v>78</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="36">
         <v>45930</v>
       </c>
-      <c r="D68" s="34" t="s">
+      <c r="D68" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="E68" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="M68" s="19" t="s">
+      <c r="E68" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="M68" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P68" t="s">
+      <c r="P68" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="Q68" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A69" s="3">
+      <c r="A69" s="29">
         <v>79</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="36">
         <v>45930</v>
       </c>
-      <c r="D69" s="34" t="s">
+      <c r="D69" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="E69" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="G69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="M69" s="22" t="s">
+      <c r="E69" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="M69" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="P69" t="s">
+      <c r="P69" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="Q69" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A70" s="3">
+      <c r="A70" s="29">
         <v>80</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="36">
         <v>45930</v>
       </c>
-      <c r="D70" s="34" t="s">
+      <c r="D70" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="E70" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="G70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="M70" s="22" t="s">
+      <c r="E70" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="M70" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="P70" t="s">
+      <c r="P70" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="Q70" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A71" s="3">
+      <c r="A71" s="29">
         <v>82</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="36">
         <v>46066</v>
       </c>
-      <c r="D71" s="34" t="s">
+      <c r="D71" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="E71" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="E71" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G71" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="H71" s="19" t="s">
+      <c r="H71" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="M71" s="19" t="s">
+      <c r="M71" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P71" t="s">
+      <c r="P71" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="Q71" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R71">
+      <c r="R71" s="22">
         <v>2</v>
       </c>
-      <c r="S71" t="s">
+      <c r="S71" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A72" s="3">
+      <c r="A72" s="29">
         <v>83</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="36">
         <v>46069</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="E72" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="G72" s="19" t="s">
+      <c r="E72" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G72" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="H72" s="19" t="s">
+      <c r="H72" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="M72" s="19" t="s">
+      <c r="M72" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="P72" t="s">
+      <c r="P72" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="Q72" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="R72">
+      <c r="R72" s="22">
         <v>1</v>
       </c>
-      <c r="S72" t="s">
+      <c r="S72" s="22" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A73" s="3">
+      <c r="A73" s="29">
         <v>84</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="36">
         <v>46240</v>
       </c>
-      <c r="D73" s="36" t="s">
+      <c r="D73" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="E73" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="G73" s="19" t="s">
+      <c r="E73" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G73" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="H73" s="19" t="s">
+      <c r="H73" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="M73" s="22" t="s">
+      <c r="I73" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="M73" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P73" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="Q73" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A74" s="29">
+        <v>85</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="36">
+        <v>46241</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="I74" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="M74" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="P74" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q74" s="22" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3993,7 +3936,7 @@
     <sortCondition ref="A2:A42"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36:B39 B41 B32:B34 B2:B28 B61:B70 B73" xr:uid="{ED44EAAA-DACA-40E8-A7DB-D96063B10E1E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36:B39 B41 B32:B34 B2:B28 B61:B70 B73:B74" xr:uid="{ED44EAAA-DACA-40E8-A7DB-D96063B10E1E}">
       <formula1>$T$3:$T$8</formula1>
     </dataValidation>
   </dataValidations>
@@ -4072,7 +4015,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="25"/>
+      <c r="A11" s="16"/>
       <c r="B11" t="s">
         <v>47</v>
       </c>
@@ -4288,37 +4231,37 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="13" t="s">
         <v>111</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -4351,31 +4294,31 @@
       <c r="B3" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="9">
         <v>45893</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19" t="s">
+      <c r="E3" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19" t="s">
+      <c r="N3" s="11"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="16" t="s">
         <v>135</v>
       </c>
       <c r="R3">
